--- a/artfynd/A 14458-2026 artfynd.xlsx
+++ b/artfynd/A 14458-2026 artfynd.xlsx
@@ -775,7 +775,7 @@
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson, Sture Gustafsson, Erik Kilander</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
@@ -886,7 +886,7 @@
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson, Sture Gustafsson, Erik Kilander</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
@@ -997,7 +997,7 @@
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson, Sture Gustafsson, Erik Kilander</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson, Sture Gustafsson, Erik Kilander</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
@@ -1224,7 +1224,7 @@
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson, Sture Gustafsson, Erik Kilander</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson, Sture Gustafsson, Erik Kilander</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
@@ -1464,7 +1464,7 @@
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson, Sture Gustafsson, Erik Kilander</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Alva Danielsson, Sture Gustafsson</t>
+          <t>Alva Danielsson, Sture Gustafsson, Erik Kilander</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">

--- a/artfynd/A 14458-2026 artfynd.xlsx
+++ b/artfynd/A 14458-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -783,6 +788,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446038</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -894,6 +904,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446041</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1005,6 +1020,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446034</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1116,6 +1136,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446042</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1232,6 +1257,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446030</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1351,6 +1381,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446032</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1472,6 +1507,11 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446035</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1600,8 +1640,23 @@
           <t>Naturskyddsföreningen Västerbottens naturvärdesinventeringar 2026</t>
         </is>
       </c>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135446033</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/A 14458-2026 artfynd.xlsx
+++ b/artfynd/A 14458-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135446038</v>
       </c>
       <c r="B2" t="n">
-        <v>79373</v>
+        <v>79411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135446041</v>
       </c>
       <c r="B3" t="n">
-        <v>79992</v>
+        <v>80030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135446034</v>
       </c>
       <c r="B4" t="n">
-        <v>80382</v>
+        <v>80420</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135446042</v>
       </c>
       <c r="B5" t="n">
-        <v>80500</v>
+        <v>80538</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135446030</v>
       </c>
       <c r="B6" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135446032</v>
       </c>
       <c r="B7" t="n">
-        <v>57972</v>
+        <v>57977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>135446035</v>
       </c>
       <c r="B8" t="n">
-        <v>58136</v>
+        <v>58141</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>135446033</v>
       </c>
       <c r="B9" t="n">
-        <v>99195</v>
+        <v>99242</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14458-2026 artfynd.xlsx
+++ b/artfynd/A 14458-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135446038</v>
       </c>
       <c r="B2" t="n">
-        <v>79411</v>
+        <v>79438</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135446041</v>
       </c>
       <c r="B3" t="n">
-        <v>80030</v>
+        <v>80057</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135446034</v>
       </c>
       <c r="B4" t="n">
-        <v>80420</v>
+        <v>80447</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135446042</v>
       </c>
       <c r="B5" t="n">
-        <v>80538</v>
+        <v>80565</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>135446033</v>
       </c>
       <c r="B9" t="n">
-        <v>99242</v>
+        <v>99269</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14458-2026 artfynd.xlsx
+++ b/artfynd/A 14458-2026 artfynd.xlsx
@@ -1518,7 +1518,7 @@
         <v>135446033</v>
       </c>
       <c r="B9" t="n">
-        <v>99274</v>
+        <v>99276</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 14458-2026 artfynd.xlsx
+++ b/artfynd/A 14458-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>135446038</v>
       </c>
       <c r="B2" t="n">
-        <v>79441</v>
+        <v>79443</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -799,7 +799,7 @@
         <v>135446041</v>
       </c>
       <c r="B3" t="n">
-        <v>80060</v>
+        <v>80062</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -915,7 +915,7 @@
         <v>135446034</v>
       </c>
       <c r="B4" t="n">
-        <v>80450</v>
+        <v>80452</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1031,7 +1031,7 @@
         <v>135446042</v>
       </c>
       <c r="B5" t="n">
-        <v>80568</v>
+        <v>80570</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1147,7 +1147,7 @@
         <v>135446030</v>
       </c>
       <c r="B6" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1268,7 +1268,7 @@
         <v>135446032</v>
       </c>
       <c r="B7" t="n">
-        <v>57977</v>
+        <v>57979</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1392,7 +1392,7 @@
         <v>135446035</v>
       </c>
       <c r="B8" t="n">
-        <v>58141</v>
+        <v>58143</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1518,7 +1518,7 @@
         <v>135446033</v>
       </c>
       <c r="B9" t="n">
-        <v>99276</v>
+        <v>99293</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
